--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484060_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484060_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7703</v>
+        <v>5.9475</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9107</v>
+        <v>2.7892</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8597</v>
+        <v>3.1583</v>
       </c>
       <c r="G2" t="n">
         <v>2.7323</v>
@@ -610,13 +610,13 @@
         <v>2.9758</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3995</v>
+        <v>0.5767</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4963</v>
+        <v>-0.6177</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8958</v>
+        <v>1.1944</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3373</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4045</v>
+        <v>5.1914</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0203</v>
+        <v>3.4705</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3842</v>
+        <v>1.7209</v>
       </c>
       <c r="G3" t="n">
         <v>1.0643</v>
@@ -688,13 +688,13 @@
         <v>2.9758</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3322</v>
+        <v>0.119</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2382</v>
+        <v>-0.3117</v>
       </c>
       <c r="U3" t="n">
-        <v>0.094</v>
+        <v>0.4307</v>
       </c>
       <c r="V3" t="n">
         <v>3.0162</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2156</v>
+        <v>2.1911</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3335</v>
+        <v>-0.895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8821</v>
+        <v>3.0861</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1475</v>
+        <v>1.1052</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3328</v>
+        <v>0.7154</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1853</v>
+        <v>0.3898</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2904</v>
+        <v>1.3778</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.277</v>
+        <v>0.3533</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5674</v>
+        <v>1.0245</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4379</v>
+        <v>-0.2726</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0558</v>
+        <v>0.3621</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3821</v>
+        <v>-0.6347</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7935</v>
+        <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2243</v>
+        <v>0.7567</v>
       </c>
       <c r="T4" t="n">
-        <v>2.035</v>
+        <v>-0.289</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1893</v>
+        <v>1.0456</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9401</v>
+        <v>1.3801</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9776</v>
+        <v>0.2735</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9177</v>
+        <v>1.1066</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1052</v>
+        <v>-0.1475</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7154</v>
+        <v>-0.3328</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3898</v>
+        <v>0.1853</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3778</v>
+        <v>0.2904</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3533</v>
+        <v>-0.277</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0245</v>
+        <v>0.5674</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2726</v>
+        <v>-0.4379</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3621</v>
+        <v>-0.0558</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6347</v>
+        <v>-0.3821</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>2.579</v>
+        <v>0.7935</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4943</v>
+        <v>1.3887</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3716</v>
+        <v>0.975</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8773</v>
+        <v>0.4137</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>0.3373</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2508</v>
+        <v>0.4216</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4928</v>
+        <v>-1.6699</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.242</v>
+        <v>2.0915</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2585</v>
+        <v>1.757</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4309</v>
+        <v>0.7309</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6893</v>
+        <v>1.0261</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2895</v>
+        <v>1.6459</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1263</v>
+        <v>0.9179</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1632</v>
+        <v>0.728</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.548</v>
+        <v>0.1111</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3046</v>
+        <v>-0.187</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8525</v>
+        <v>0.2981</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5871</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R6" t="n">
-        <v>2.579</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1287</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0112</v>
+        <v>-0.34</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1399</v>
+        <v>0.8657</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2065</v>
+        <v>-0.8692</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4129</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09180000000000001</v>
+        <v>-0.021</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6362</v>
+        <v>0.2491</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5443</v>
+        <v>-0.2701</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6456</v>
+        <v>-0.2585</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2871</v>
+        <v>1.4309</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9328</v>
+        <v>-1.6893</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0806</v>
+        <v>0.2895</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0806</v>
+        <v>0.1263</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1632</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.548</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2065</v>
+        <v>1.3046</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9328</v>
+        <v>-1.8525</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1984</v>
+        <v>2.579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.539</v>
+        <v>-0.1431</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5555</v>
+        <v>-0.2549</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0165</v>
+        <v>0.1118</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1331</v>
+        <v>-0.4005</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1404</v>
+        <v>0.228</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0073</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>1.757</v>
+        <v>-0.6456</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7309</v>
+        <v>0.2871</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0261</v>
+        <v>-0.9328</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6459</v>
+        <v>0.0806</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9179</v>
+        <v>0.0806</v>
       </c>
       <c r="L8" t="n">
-        <v>0.728</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1111</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.187</v>
+        <v>0.2065</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2981</v>
+        <v>-0.9328</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9838</v>
+        <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0289</v>
+        <v>0.0468</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8105</v>
+        <v>0.1474</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7816</v>
+        <v>-0.1006</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5088</v>
+        <v>-1.9605</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7076</v>
+        <v>-0.991</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8012</v>
+        <v>-0.9695</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2047</v>
@@ -1234,13 +1234,13 @@
         <v>1.5871</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2992</v>
+        <v>0.8474</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9807</v>
+        <v>0.6973</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3184</v>
+        <v>0.1501</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3928</v>
+        <v>-2.4876</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2841</v>
+        <v>-2.5472</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1087</v>
+        <v>0.0596</v>
       </c>
       <c r="G11" t="n">
         <v>1.4574</v>
@@ -1312,13 +1312,13 @@
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7437</v>
+        <v>0.1615</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6858</v>
+        <v>0.0511</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0579</v>
+        <v>0.1105</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3373</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.1793</v>
+        <v>8.803000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7080999999999995</v>
+        <v>-0.08469999999999978</v>
       </c>
       <c r="F12" t="n">
-        <v>8.887599999999999</v>
+        <v>8.887699999999999</v>
       </c>
       <c r="G12" t="n">
         <v>5.3927</v>
@@ -1390,10 +1390,10 @@
         <v>16.8627</v>
       </c>
       <c r="S12" t="n">
-        <v>3.656</v>
+        <v>4.2794</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5659999999999997</v>
+        <v>0.05749999999999996</v>
       </c>
       <c r="U12" t="n">
         <v>4.2219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7597</v>
+        <v>4.4024</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6556</v>
+        <v>2.9617</v>
       </c>
       <c r="F13" t="n">
-        <v>1.104</v>
+        <v>1.4407</v>
       </c>
       <c r="G13" t="n">
         <v>1.5701</v>
@@ -1468,13 +1468,13 @@
         <v>3.1741</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4136</v>
+        <v>-0.7709</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7537</v>
+        <v>-0.4477</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6599</v>
+        <v>-0.3232</v>
       </c>
       <c r="V13" t="n">
         <v>2.4129</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3491</v>
+        <v>0.0022</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8385</v>
+        <v>-0.7365</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1876</v>
+        <v>0.7387</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6993</v>
@@ -1546,13 +1546,13 @@
         <v>3.1741</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.305</v>
+        <v>-0.6519</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1278</v>
+        <v>-1.0258</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8228</v>
+        <v>0.3739</v>
       </c>
       <c r="V14" t="n">
         <v>2.1469</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1661</v>
+        <v>-1.5075</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.2177</v>
+        <v>-1.1079</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0516</v>
+        <v>-0.3996</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.5281</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.8197</v>
+        <v>-0.6046</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2916</v>
+        <v>1.1958</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.7867</v>
+        <v>1.7326</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.0328</v>
+        <v>-0.0849</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2461</v>
+        <v>1.8175</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-1.1414</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7869</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0455</v>
+        <v>-0.6217</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3806</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6993</v>
+        <v>-1.3051</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2868</v>
+        <v>-1.0711</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4125</v>
+        <v>-0.2339</v>
       </c>
       <c r="V15" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.4282</v>
+        <v>-2.499</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.72</v>
+        <v>-2.5102</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7082000000000001</v>
+        <v>0.0112</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5911999999999999</v>
+        <v>-2.6252</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6046</v>
+        <v>-0.3631</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1958</v>
+        <v>-2.2621</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7326</v>
+        <v>-1.0989</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0849</v>
+        <v>0.1008</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8175</v>
+        <v>-1.1997</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1414</v>
+        <v>-1.5262</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.4639</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6217</v>
+        <v>-1.0623</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2259</v>
+        <v>-0.0723</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.6833</v>
+        <v>-0.4194</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5425</v>
+        <v>0.3471</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.6189</v>
+        <v>-2.7832</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7143</v>
+        <v>-4.4421</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0954</v>
+        <v>1.6589</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.6252</v>
+        <v>-3.5281</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3631</v>
+        <v>-3.8197</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2621</v>
+        <v>0.2916</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0989</v>
+        <v>-2.7867</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1008</v>
+        <v>-3.0328</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1997</v>
+        <v>0.2461</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5262</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4639</v>
+        <v>-0.7869</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0623</v>
+        <v>0.0455</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1903</v>
+        <v>2.3806</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1921</v>
+        <v>0.0822</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4313</v>
+        <v>0.0197</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. GUILLET</t>
+          <t>J. MIRANDA VARGAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9642</v>
+        <v>-2.8429</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6611</v>
+        <v>-4.3056</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.6253</v>
+        <v>1.4627</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9555</v>
+        <v>-1.6568</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3156</v>
+        <v>-1.3356</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2711</v>
+        <v>-0.3213</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8687</v>
+        <v>-0.304</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6908</v>
+        <v>-1.5567</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1779</v>
+        <v>1.2527</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9132</v>
+        <v>-1.3528</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0064</v>
+        <v>0.2212</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-1.574</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3968</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R18" t="n">
         <v>2.3806</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3598</v>
+        <v>-0.5909</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1135</v>
+        <v>-1.0258</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4733</v>
+        <v>0.4349</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.9566</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.6194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MIRANDA VARGAS</t>
+          <t>K. GUILLET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1108</v>
+        <v>-2.9515</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.7137</v>
+        <v>1.2529</v>
       </c>
       <c r="F19" t="n">
-        <v>1.603</v>
+        <v>-4.2044</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6568</v>
+        <v>0.9555</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3356</v>
+        <v>-1.3156</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3213</v>
+        <v>2.2711</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.304</v>
+        <v>3.8687</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5567</v>
+        <v>0.6908</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2527</v>
+        <v>3.1779</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3528</v>
+        <v>-2.9132</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2212</v>
+        <v>-2.0064</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.574</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
         <v>2.3806</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8588</v>
+        <v>-0.3471</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4339</v>
+        <v>-0.2946</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5752</v>
+        <v>-0.0525</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-3.9566</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="20">
@@ -1969,16 +1969,16 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.179399999999999</v>
+        <v>-8.179499999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.887499999999999</v>
+        <v>-8.887699999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7080999999999993</v>
+        <v>0.7082000000000006</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.3926</v>
+        <v>-5.392600000000001</v>
       </c>
       <c r="H20" t="n">
         <v>-8.1135</v>
@@ -1999,13 +1999,13 @@
         <v>-11.3626</v>
       </c>
       <c r="N20" t="n">
-        <v>-5.598300000000001</v>
+        <v>-5.5983</v>
       </c>
       <c r="O20" t="n">
         <v>-5.7643</v>
       </c>
       <c r="P20" t="n">
-        <v>9.999999999987796e-05</v>
+        <v>9.999999999993348e-05</v>
       </c>
       <c r="Q20" t="n">
         <v>-16.8626</v>
@@ -2014,13 +2014,13 @@
         <v>16.8625</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.6559</v>
+        <v>-3.656</v>
       </c>
       <c r="T20" t="n">
         <v>-4.2219</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5661</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0.8692000000000002</v>
